--- a/outputs/54925.xlsx
+++ b/outputs/54925.xlsx
@@ -259,12 +259,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
-        <bgColor rgb="FF33CCCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
@@ -273,6 +267,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor rgb="FF339966"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
+        <bgColor rgb="FF33CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -310,7 +310,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -323,11 +323,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -343,29 +343,25 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -667,7 +663,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q41"/>
+  <dimension ref="A1:Q40"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
@@ -762,7 +758,8 @@
       <c r="N2" s="5"/>
       <c r="O2" s="5"/>
       <c r="Q2" s="6" t="n">
-        <v>8002468</v>
+        <f aca="false" t="array" ref="Q2:Q2">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
+        <v>8002107</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -797,16 +794,16 @@
       <c r="N3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="O3" s="8"/>
-      <c r="Q3" s="9" t="n">
-        <v>8002578</v>
+      <c r="Q3" s="6" t="n">
+        <f aca="false" t="array" ref="Q3:Q3">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
+        <v>8002104</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="10" t="n">
+      <c r="B4" s="8" t="n">
         <v>8002468</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -818,22 +815,22 @@
         <v>12</v>
       </c>
       <c r="G4" s="3"/>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="9" t="s">
         <v>4</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>20</v>
       </c>
       <c r="J4" s="3"/>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="9" t="s">
         <v>17</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="O4" s="8"/>
-      <c r="Q4" s="9" t="n">
-        <v>8002404</v>
+      <c r="Q4" s="6" t="n">
+        <f aca="false" t="array" ref="Q4:Q4">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
+        <v>8002578</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -864,16 +861,16 @@
       <c r="K5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O5" s="8"/>
-      <c r="Q5" s="9" t="n">
-        <v>8002577</v>
+      <c r="Q5" s="6" t="n">
+        <f aca="false" t="array" ref="Q5:Q5">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
+        <v>8002223</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="10" t="n">
         <v>8002578</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -885,26 +882,26 @@
         <v>12</v>
       </c>
       <c r="G6" s="3"/>
-      <c r="H6" s="13" t="s">
+      <c r="H6" s="11" t="s">
         <v>4</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>20</v>
       </c>
       <c r="J6" s="3"/>
-      <c r="K6" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="O6" s="8"/>
-      <c r="Q6" s="9" t="n">
-        <v>8002224</v>
+      <c r="K6" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <f aca="false" t="array" ref="Q6:Q6">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
+        <v>8002026</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="10" t="n">
         <v>8002404</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -916,19 +913,19 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="13" t="s">
+      <c r="H7" s="11" t="s">
         <v>4</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>20</v>
       </c>
       <c r="J7" s="3"/>
-      <c r="K7" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="O7" s="8"/>
-      <c r="Q7" s="9" t="n">
-        <v>8002430</v>
+      <c r="K7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <f aca="false" t="array" ref="Q7:Q7">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
+        <v>8002224</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -959,9 +956,9 @@
       <c r="K8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="O8" s="8"/>
-      <c r="Q8" s="9" t="n">
-        <v>8002450</v>
+      <c r="Q8" s="6" t="n">
+        <f aca="false" t="array" ref="Q8:Q8">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
+        <v>8002430</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -990,9 +987,9 @@
       <c r="K9" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O9" s="8"/>
-      <c r="Q9" s="9" t="n">
-        <v>8002427</v>
+      <c r="Q9" s="12" t="n">
+        <f aca="false" t="array" ref="Q9:Q9">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
+        <v>8002445</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1021,9 +1018,9 @@
       <c r="K10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O10" s="8"/>
       <c r="Q10" s="6" t="n">
-        <v>8002588</v>
+        <f aca="false" t="array" ref="Q10:Q10">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
+        <v>8002204</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1052,9 +1049,9 @@
       <c r="K11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O11" s="8"/>
-      <c r="Q11" s="9" t="n">
-        <v>8002443</v>
+      <c r="Q11" s="6" t="n">
+        <f aca="false" t="array" ref="Q11:Q11">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
+        <v>8002434</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1085,16 +1082,16 @@
       <c r="K12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O12" s="8"/>
-      <c r="Q12" s="9" t="n">
-        <v>8002562</v>
+      <c r="Q12" s="12" t="n">
+        <f aca="false" t="array" ref="Q12:Q12">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
+        <v>8002443</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="12" t="n">
+      <c r="B13" s="10" t="n">
         <v>8002577</v>
       </c>
       <c r="C13" s="3" t="s">
@@ -1106,7 +1103,7 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="13" t="s">
+      <c r="H13" s="11" t="s">
         <v>4</v>
       </c>
       <c r="I13" s="4" t="s">
@@ -1115,10 +1112,9 @@
       <c r="J13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K13" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="O13" s="8"/>
+      <c r="K13" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="Q13" s="1" t="str">
         <f aca="false" t="array" ref="Q13:Q13">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
         <v/>
@@ -1150,7 +1146,6 @@
       <c r="K14" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O14" s="8"/>
       <c r="Q14" s="1" t="str">
         <f aca="false" t="array" ref="Q14:Q14">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
         <v/>
@@ -1182,7 +1177,6 @@
       <c r="K15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O15" s="8"/>
       <c r="Q15" s="1" t="str">
         <f aca="false" t="array" ref="Q15:Q15">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
         <v/>
@@ -1216,7 +1210,6 @@
       <c r="K16" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="O16" s="8"/>
       <c r="Q16" s="1" t="str">
         <f aca="false" t="array" ref="Q16:Q16">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
         <v/>
@@ -1250,7 +1243,6 @@
       <c r="K17" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="O17" s="8"/>
       <c r="Q17" s="1" t="str">
         <f aca="false" t="array" ref="Q17:Q17">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
         <v/>
@@ -1282,7 +1274,6 @@
       <c r="K18" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O18" s="8"/>
       <c r="Q18" s="1" t="str">
         <f aca="false" t="array" ref="Q18:Q18">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
         <v/>
@@ -1318,7 +1309,6 @@
       <c r="K19" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O19" s="8"/>
       <c r="Q19" s="1" t="str">
         <f aca="false" t="array" ref="Q19:Q19">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
         <v/>
@@ -1350,7 +1340,6 @@
       <c r="K20" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O20" s="8"/>
       <c r="Q20" s="1" t="str">
         <f aca="false" t="array" ref="Q20:Q20">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
         <v/>
@@ -1360,7 +1349,7 @@
       <c r="A21" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="12" t="n">
+      <c r="B21" s="10" t="n">
         <v>8002224</v>
       </c>
       <c r="C21" s="3" t="s">
@@ -1372,17 +1361,16 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
-      <c r="H21" s="13" t="s">
+      <c r="H21" s="11" t="s">
         <v>4</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>30</v>
       </c>
       <c r="J21" s="3"/>
-      <c r="K21" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="O21" s="8"/>
+      <c r="K21" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="Q21" s="1" t="str">
         <f aca="false" t="array" ref="Q21:Q21">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
         <v/>
@@ -1392,7 +1380,7 @@
       <c r="A22" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="12" t="n">
+      <c r="B22" s="10" t="n">
         <v>8002430</v>
       </c>
       <c r="C22" s="3" t="s">
@@ -1404,17 +1392,16 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
-      <c r="H22" s="13" t="s">
+      <c r="H22" s="11" t="s">
         <v>4</v>
       </c>
       <c r="I22" s="4" t="s">
         <v>20</v>
       </c>
       <c r="J22" s="3"/>
-      <c r="K22" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="O22" s="8"/>
+      <c r="K22" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="Q22" s="1" t="str">
         <f aca="false" t="array" ref="Q22:Q22">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
         <v/>
@@ -1424,7 +1411,7 @@
       <c r="A23" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="12" t="n">
+      <c r="B23" s="10" t="n">
         <v>8002450</v>
       </c>
       <c r="C23" s="3" t="s">
@@ -1436,17 +1423,16 @@
         <v>12</v>
       </c>
       <c r="G23" s="3"/>
-      <c r="H23" s="13" t="s">
+      <c r="H23" s="11" t="s">
         <v>4</v>
       </c>
       <c r="I23" s="4" t="s">
         <v>20</v>
       </c>
       <c r="J23" s="3"/>
-      <c r="K23" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="O23" s="8"/>
+      <c r="K23" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="Q23" s="1" t="str">
         <f aca="false" t="array" ref="Q23:Q23">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
         <v/>
@@ -1476,7 +1462,6 @@
       <c r="K24" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O24" s="8"/>
       <c r="Q24" s="1" t="str">
         <f aca="false" t="array" ref="Q24:Q24">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
         <v/>
@@ -1506,7 +1491,6 @@
       <c r="K25" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="O25" s="8"/>
       <c r="Q25" s="1" t="str">
         <f aca="false" t="array" ref="Q25:Q25">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
         <v/>
@@ -1516,7 +1500,7 @@
       <c r="A26" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="12" t="n">
+      <c r="B26" s="10" t="n">
         <v>8002427</v>
       </c>
       <c r="C26" s="3" t="s">
@@ -1528,17 +1512,16 @@
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
-      <c r="H26" s="13" t="s">
+      <c r="H26" s="11" t="s">
         <v>4</v>
       </c>
       <c r="I26" s="4" t="s">
         <v>20</v>
       </c>
       <c r="J26" s="3"/>
-      <c r="K26" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="O26" s="8"/>
+      <c r="K26" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="Q26" s="1" t="str">
         <f aca="false" t="array" ref="Q26:Q26">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
         <v/>
@@ -1570,7 +1553,6 @@
       <c r="K27" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O27" s="8"/>
       <c r="Q27" s="1" t="str">
         <f aca="false" t="array" ref="Q27:Q27">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
         <v/>
@@ -1606,7 +1588,6 @@
       <c r="K28" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O28" s="8"/>
       <c r="Q28" s="1" t="str">
         <f aca="false" t="array" ref="Q28:Q28">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
         <v/>
@@ -1638,7 +1619,6 @@
       <c r="K29" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O29" s="8"/>
       <c r="Q29" s="1" t="str">
         <f aca="false" t="array" ref="Q29:Q29">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
         <v/>
@@ -1674,7 +1654,6 @@
       <c r="K30" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O30" s="8"/>
       <c r="Q30" s="1" t="str">
         <f aca="false" t="array" ref="Q30:Q30">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
         <v/>
@@ -1708,7 +1687,6 @@
       <c r="K31" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O31" s="8"/>
       <c r="Q31" s="1" t="str">
         <f aca="false" t="array" ref="Q31:Q31">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
         <v/>
@@ -1740,7 +1718,6 @@
       <c r="K32" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O32" s="8"/>
       <c r="Q32" s="1" t="str">
         <f aca="false" t="array" ref="Q32:Q32">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
         <v/>
@@ -1772,7 +1749,6 @@
       <c r="K33" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="O33" s="8"/>
       <c r="Q33" s="1" t="str">
         <f aca="false" t="array" ref="Q33:Q33">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
         <v/>
@@ -1806,7 +1782,6 @@
       <c r="K34" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="O34" s="8"/>
       <c r="Q34" s="1" t="str">
         <f aca="false" t="array" ref="Q34:Q34">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
         <v/>
@@ -1842,7 +1817,6 @@
       <c r="K35" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O35" s="8"/>
       <c r="Q35" s="1" t="str">
         <f aca="false" t="array" ref="Q35:Q35">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
         <v/>
@@ -1874,7 +1848,6 @@
       <c r="K36" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O36" s="8"/>
       <c r="Q36" s="1" t="str">
         <f aca="false" t="array" ref="Q36:Q36">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
         <v/>
@@ -1884,7 +1857,7 @@
       <c r="A37" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B37" s="10" t="n">
+      <c r="B37" s="8" t="n">
         <v>8002588</v>
       </c>
       <c r="C37" s="3" t="s">
@@ -1896,17 +1869,16 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
-      <c r="H37" s="11" t="s">
+      <c r="H37" s="9" t="s">
         <v>4</v>
       </c>
       <c r="I37" s="4" t="s">
         <v>20</v>
       </c>
       <c r="J37" s="3"/>
-      <c r="K37" s="11" t="s">
+      <c r="K37" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O37" s="8"/>
       <c r="Q37" s="1" t="str">
         <f aca="false" t="array" ref="Q37:Q37">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
         <v/>
@@ -1938,7 +1910,6 @@
       <c r="K38" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="O38" s="8"/>
       <c r="Q38" s="1" t="str">
         <f aca="false" t="array" ref="Q38:Q38">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
         <v/>
@@ -1948,7 +1919,7 @@
       <c r="A39" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B39" s="12" t="n">
+      <c r="B39" s="10" t="n">
         <v>8002443</v>
       </c>
       <c r="C39" s="3" t="s">
@@ -1960,17 +1931,16 @@
         <v>12</v>
       </c>
       <c r="G39" s="3"/>
-      <c r="H39" s="13" t="s">
+      <c r="H39" s="11" t="s">
         <v>4</v>
       </c>
       <c r="I39" s="4" t="s">
         <v>20</v>
       </c>
       <c r="J39" s="3"/>
-      <c r="K39" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="O39" s="8"/>
+      <c r="K39" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="Q39" s="1" t="str">
         <f aca="false" t="array" ref="Q39:Q39">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
         <v/>
@@ -1980,7 +1950,7 @@
       <c r="A40" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B40" s="12" t="n">
+      <c r="B40" s="10" t="n">
         <v>8002562</v>
       </c>
       <c r="C40" s="3" t="s">
@@ -1992,24 +1962,20 @@
         <v>12</v>
       </c>
       <c r="G40" s="3"/>
-      <c r="H40" s="13" t="s">
+      <c r="H40" s="11" t="s">
         <v>4</v>
       </c>
       <c r="I40" s="4" t="s">
         <v>20</v>
       </c>
       <c r="J40" s="3"/>
-      <c r="K40" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="O40" s="8"/>
+      <c r="K40" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="Q40" s="1" t="str">
         <f aca="false" t="array" ref="Q40:Q40">IFERROR(INDEX($B$2:$B$40,SMALL(IF(0&lt;($M$3=$H$2:$H$40)*(($N$3=$K$2:$K$40)+($N$4=$K$2:$K$40)),ROW($B$2:$B$40)-2,""),ROW()-1)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="O41" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">
